--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E708624E-64F9-43D5-980B-A02F1DF4A3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B4FD9B-152E-4432-B3ED-C99A844950E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7650" yWindow="2370" windowWidth="16620" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -700,53 +700,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4845_7_0</t>
-  </si>
-  <si>
-    <t>4845_7_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>22</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -791,6 +744,42 @@
   <si>
     <t>剑兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4846-8/4846-8_0</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_1</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_2</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_3</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_4</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_9</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_10</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_11</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_5</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_8</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_6</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_7</t>
   </si>
 </sst>
 </file>
@@ -1287,38 +1276,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.25" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.26953125" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="76.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="76.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1397,7 +1386,7 @@
         <v>49</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="AC1" s="6" t="s">
         <v>62</v>
@@ -1418,7 +1407,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1458,7 +1447,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1539,10 +1528,10 @@
         <v>52</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7" t="s">
@@ -1560,7 +1549,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1643,7 +1632,7 @@
         <v>55</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="AC4" s="10" t="s">
         <v>63</v>
@@ -1664,18 +1653,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>65</v>
@@ -1731,7 +1720,7 @@
         <v>27</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>111</v>
@@ -1741,7 +1730,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1806,7 +1795,7 @@
         <v>53</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AC6" s="2" t="s">
         <v>66</v>
@@ -1815,7 +1804,7 @@
         <v>28</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>112</v>
@@ -1825,18 +1814,18 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>117</v>
@@ -1889,7 +1878,7 @@
         <v>53</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>66</v>
@@ -1898,7 +1887,7 @@
         <v>29</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>113</v>
@@ -1908,18 +1897,18 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>120</v>
@@ -1981,7 +1970,7 @@
         <v>30</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>114</v>
@@ -1991,7 +1980,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2055,19 +2044,19 @@
         <v>53</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="AE9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>115</v>
@@ -2077,7 +2066,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2133,7 +2122,7 @@
         <v>53</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC10" s="2" t="s">
         <v>66</v>
@@ -2146,7 +2135,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2202,7 +2191,7 @@
         <v>53</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC11" s="2" t="s">
         <v>66</v>
@@ -2215,7 +2204,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2272,7 +2261,7 @@
         <v>54</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC12" s="2" t="s">
         <v>66</v>
@@ -2281,14 +2270,14 @@
         <v>36</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>140</v>
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2348,7 +2337,7 @@
         <v>54</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>66</v>
@@ -2357,14 +2346,14 @@
         <v>37</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2424,7 +2413,7 @@
         <v>54</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC14" s="2" t="s">
         <v>66</v>
@@ -2433,14 +2422,14 @@
         <v>38</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>142</v>
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2503,7 +2492,7 @@
         <v>53</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC15" s="2" t="s">
         <v>66</v>
@@ -2512,7 +2501,7 @@
         <v>32</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="AG15" s="2" t="s">
         <v>154</v>
@@ -2522,7 +2511,7 @@
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2585,7 +2574,7 @@
         <v>53</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC16" s="2" t="s">
         <v>66</v>
@@ -2594,7 +2583,7 @@
         <v>35</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AG16" s="2" t="s">
         <v>154</v>
@@ -2604,7 +2593,7 @@
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2667,7 +2656,7 @@
         <v>53</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC17" s="2" t="s">
         <v>66</v>
@@ -2676,7 +2665,7 @@
         <v>33</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>155</v>
@@ -2686,7 +2675,7 @@
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2749,7 +2738,7 @@
         <v>53</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC18" s="2" t="s">
         <v>66</v>
@@ -2758,7 +2747,7 @@
         <v>34</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>155</v>
@@ -2768,7 +2757,7 @@
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2795,7 +2784,7 @@
         <v>126</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>67</v>
@@ -2807,13 +2796,13 @@
         <v>8</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2840,7 +2829,7 @@
         <v>125</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>67</v>
@@ -2852,13 +2841,13 @@
         <v>13</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2885,7 +2874,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>67</v>
@@ -2897,13 +2886,13 @@
         <v>16</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2930,7 +2919,7 @@
         <v>126</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>65</v>
@@ -2942,13 +2931,13 @@
         <v>9</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -2975,7 +2964,7 @@
         <v>125</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>65</v>
@@ -2987,13 +2976,13 @@
         <v>10</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3020,7 +3009,7 @@
         <v>125</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>65</v>
@@ -3032,13 +3021,13 @@
         <v>12</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3077,16 +3066,16 @@
         <v>11</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="AD25" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3125,16 +3114,16 @@
         <v>14</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="AD26" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3173,16 +3162,16 @@
         <v>15</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC27" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="AD27" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3221,18 +3210,18 @@
         <v>17</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3259,7 +3248,7 @@
         <v>125</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>68</v>
@@ -3274,12 +3263,12 @@
         <v>70</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3306,7 +3295,7 @@
         <v>125</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>68</v>
@@ -3321,10 +3310,10 @@
         <v>70</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3332,7 +3321,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3353,7 +3342,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3374,159 +3363,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>
